--- a/shards/tests/data/spreadsheet_test.xlsx
+++ b/shards/tests/data/spreadsheet_test.xlsx
@@ -10,6 +10,7 @@
     <sheet name="People" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sparse" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DupHeaders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Formulas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,4 +572,72 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <f>A2+B2</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>A2*B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <f>A3+B3</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>A3*B3</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>